--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488155_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488155_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6693</v>
+        <v>4.2563</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7675</v>
+        <v>1.453</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9018</v>
+        <v>2.8033</v>
       </c>
       <c r="G2" t="n">
         <v>4.5398</v>
@@ -610,13 +610,13 @@
         <v>4.4469</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8155</v>
+        <v>-0.2285</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9302</v>
+        <v>-0.2446</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1146</v>
+        <v>0.0161</v>
       </c>
       <c r="V2" t="n">
         <v>0.3155</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2533</v>
+        <v>2.7144</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2475</v>
+        <v>3.7579</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9942</v>
+        <v>-1.0435</v>
       </c>
       <c r="G3" t="n">
         <v>0.7974</v>
@@ -688,13 +688,13 @@
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4559</v>
+        <v>-0.083</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5944</v>
+        <v>0.1048</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1385</v>
+        <v>-0.1878</v>
       </c>
       <c r="V3" t="n">
         <v>1.2589</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2847</v>
+        <v>2.0156</v>
       </c>
       <c r="E4" t="n">
-        <v>0.975</v>
+        <v>0.6812</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3097</v>
+        <v>1.3344</v>
       </c>
       <c r="G4" t="n">
         <v>1.2446</v>
@@ -766,13 +766,13 @@
         <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>0.244</v>
+        <v>-0.0252</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2151</v>
+        <v>-0.0786</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0288</v>
+        <v>0.0535</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3155</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.409</v>
+        <v>1.4084</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5078</v>
+        <v>0.6057</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9012</v>
+        <v>0.8027</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5042</v>
@@ -844,13 +844,13 @@
         <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0868</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4377</v>
+        <v>-0.3398</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3509</v>
+        <v>0.2524</v>
       </c>
       <c r="V5" t="n">
         <v>1.2589</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5093</v>
+        <v>-0.3633</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3106</v>
+        <v>-0.0168</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1987</v>
+        <v>-0.3465</v>
       </c>
       <c r="G7" t="n">
         <v>-0.39</v>
@@ -1000,13 +1000,13 @@
         <v>2.2234</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1743</v>
+        <v>-0.0283</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1131</v>
+        <v>0.1806</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0612</v>
+        <v>-0.2089</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3155</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6726</v>
+        <v>-0.3777</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.6448</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2195</v>
+        <v>-1.0225</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6062</v>
@@ -1078,13 +1078,13 @@
         <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2517</v>
+        <v>0.0432</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2699</v>
+        <v>0.3678</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5215</v>
+        <v>-0.3246</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>R. ROMERO NARANJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6825</v>
+        <v>-0.9524</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8564</v>
+        <v>-0.7736</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1738</v>
+        <v>-0.1788</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1626</v>
+        <v>-3.1377</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0536</v>
+        <v>-3.4296</v>
       </c>
       <c r="I9" t="n">
-        <v>0.891</v>
+        <v>0.2919</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1032</v>
+        <v>-0.8379</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2798</v>
+        <v>-1.6365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1766</v>
+        <v>0.7986</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0594</v>
+        <v>-2.2998</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.7738</v>
+        <v>-1.7931</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7144</v>
+        <v>-0.5067</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7411</v>
+        <v>1.8529</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.891</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>4.6322</v>
+        <v>3.7057</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7389</v>
+        <v>0.018</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1379</v>
+        <v>0.3439</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3989</v>
+        <v>-0.3258</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. ROMERO NARANJO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7811</v>
+        <v>-1.1224</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5777</v>
+        <v>-3.444</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2034</v>
+        <v>2.3216</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1377</v>
+        <v>-2.1626</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.4296</v>
+        <v>-3.0536</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2919</v>
+        <v>0.891</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8379</v>
+        <v>-0.1032</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6365</v>
+        <v>-0.2798</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7986</v>
+        <v>0.1766</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2998</v>
+        <v>-2.0594</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7931</v>
+        <v>-2.7738</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5067</v>
+        <v>0.7144</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8529</v>
+        <v>-3.891</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7057</v>
+        <v>4.6322</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1893</v>
+        <v>0.2991</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5397</v>
+        <v>0.5503</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3504</v>
+        <v>-0.2512</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5708</v>
+        <v>-1.4734</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2237</v>
+        <v>-2.0279</v>
       </c>
       <c r="F11" t="n">
-        <v>0.653</v>
+        <v>0.5545</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3893</v>
@@ -1312,13 +1312,13 @@
         <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1079</v>
+        <v>-0.0106</v>
       </c>
       <c r="T11" t="n">
-        <v>0.051</v>
+        <v>0.2469</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1589</v>
+        <v>-0.2574</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4204</v>
+        <v>-2.1261</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1035</v>
+        <v>-1.9077</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3169</v>
+        <v>-0.2184</v>
       </c>
       <c r="G12" t="n">
         <v>-1.046</v>
@@ -1390,13 +1390,13 @@
         <v>1.297</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6332</v>
+        <v>-0.3389</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4377</v>
+        <v>-0.2419</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1955</v>
+        <v>-0.097</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.601699999999998</v>
+        <v>4.601499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4050999999999996</v>
+        <v>-0.4053000000000002</v>
       </c>
       <c r="F13" t="n">
         <v>5.0068</v>
@@ -1444,7 +1444,7 @@
         <v>13.4419</v>
       </c>
       <c r="K13" t="n">
-        <v>9.4876</v>
+        <v>9.487600000000002</v>
       </c>
       <c r="L13" t="n">
         <v>3.954099999999999</v>
@@ -1468,13 +1468,13 @@
         <v>25.0137</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4412999999999999</v>
+        <v>-0.4416</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8892999999999998</v>
+        <v>0.8894</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3306</v>
+        <v>-1.3307</v>
       </c>
       <c r="V13" t="n">
         <v>2.5167</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7112</v>
+        <v>2.0227</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1764</v>
+        <v>1.7196</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4652</v>
+        <v>0.3031</v>
       </c>
       <c r="G14" t="n">
-        <v>6.0224</v>
+        <v>3.7954</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9919</v>
+        <v>5.0272</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0305</v>
+        <v>-1.2318</v>
       </c>
       <c r="J14" t="n">
-        <v>8.449999999999999</v>
+        <v>4.6447</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8053</v>
+        <v>5.1316</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6447</v>
+        <v>-0.487</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4277</v>
+        <v>-0.8493000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8134</v>
+        <v>-0.1044</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6143</v>
+        <v>-0.7448</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.5205</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.6703</v>
+        <v>-2.9646</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1499</v>
+        <v>2.594</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4681</v>
+        <v>-0.1433</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1379</v>
+        <v>0.0395</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3303</v>
+        <v>-0.1828</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2589</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5177</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9001</v>
+        <v>1.803</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6216</v>
+        <v>3.6868</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2785</v>
+        <v>-1.8838</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7954</v>
+        <v>6.0224</v>
       </c>
       <c r="H15" t="n">
-        <v>5.0272</v>
+        <v>3.9919</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2318</v>
+        <v>2.0305</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6447</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1316</v>
+        <v>5.8053</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.487</v>
+        <v>2.6447</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-2.4277</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1044</v>
+        <v>-1.8134</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7448</v>
+        <v>-0.6143</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3706</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9646</v>
+        <v>-6.6703</v>
       </c>
       <c r="R15" t="n">
-        <v>2.594</v>
+        <v>3.1499</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2659</v>
+        <v>0.5599</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0584</v>
+        <v>0.6482</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2074</v>
+        <v>-0.0883</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2589</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2589</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1732</v>
+        <v>0.7803</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0267</v>
+        <v>0.8309</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1464</v>
+        <v>-0.0505</v>
       </c>
       <c r="G16" t="n">
         <v>3.3146</v>
@@ -1702,13 +1702,13 @@
         <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8411</v>
+        <v>0.4483</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9227</v>
+        <v>0.7269</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.2786</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9444</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6221</v>
+        <v>0.6854</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6221</v>
+        <v>-0.4069</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.0923</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6221</v>
+        <v>-0.8704</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.5705</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6221</v>
+        <v>-1.4408</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6221</v>
+        <v>-0.1048</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.1595</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6221</v>
+        <v>-1.2643</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.589</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.1766</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.4443</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.4492</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.6221</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5048</v>
+        <v>0.6221</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0184</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8704</v>
+        <v>0.6221</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5705</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4408</v>
+        <v>0.6221</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1048</v>
+        <v>0.6221</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1595</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2643</v>
+        <v>0.6221</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.589</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1766</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.616</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5471</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0689</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4626</v>
+        <v>0.3171</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0092</v>
+        <v>-0.4009</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4717</v>
+        <v>0.718</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1204</v>
@@ -1936,13 +1936,13 @@
         <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4887</v>
+        <v>0.3432</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9774</v>
+        <v>0.5857</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4887</v>
+        <v>-0.2425</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3144</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3533</v>
+        <v>0.1861</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1898</v>
+        <v>-0.7981</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8365</v>
+        <v>0.9842</v>
       </c>
       <c r="G20" t="n">
         <v>0.2152</v>
@@ -2014,13 +2014,13 @@
         <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4574</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1641</v>
+        <v>0.2276</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2932</v>
+        <v>-0.1455</v>
       </c>
       <c r="V20" t="n">
         <v>0.63</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.097</v>
+        <v>-0.8749</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4547</v>
+        <v>-0.5527</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6423</v>
+        <v>-0.3222</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8391</v>
@@ -2092,13 +2092,13 @@
         <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.4063</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0584</v>
+        <v>-0.1564</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.57</v>
+        <v>-0.25</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3499</v>
+        <v>-3.0824</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0656</v>
+        <v>-4.1899</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2844</v>
+        <v>1.1075</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4481</v>
+        <v>-3.3044</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8983</v>
+        <v>-1.2843</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5498</v>
+        <v>-2.0202</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1703</v>
+        <v>-1.9186</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1288</v>
+        <v>-0.6663</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>-1.2523</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6184</v>
+        <v>-1.3858</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0271</v>
+        <v>-0.618</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5913</v>
+        <v>-0.7678</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>-2.0382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9264</v>
+        <v>2.594</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0321</v>
+        <v>-0.3339</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.383</v>
+        <v>-0.2331</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3509</v>
+        <v>-0.1007</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9433</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4401</v>
+        <v>-3.4484</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4521</v>
+        <v>-2.0656</v>
       </c>
       <c r="F23" t="n">
-        <v>0.012</v>
+        <v>-1.3829</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3551</v>
+        <v>-1.4481</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6086</v>
+        <v>-0.8983</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.5498</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3854</v>
+        <v>0.1703</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1845</v>
+        <v>0.1288</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5699</v>
+        <v>0.0415</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9697</v>
+        <v>-1.6184</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7931</v>
+        <v>-1.0271</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1766</v>
+        <v>-0.5913</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0382</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6387</v>
+        <v>-0.1306</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3246</v>
+        <v>-0.383</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3141</v>
+        <v>0.2524</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3144</v>
+        <v>-0.9433</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7439</v>
+        <v>-3.6125</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7775</v>
+        <v>-3.4521</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0336</v>
+        <v>-0.1604</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3044</v>
+        <v>-2.3551</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2843</v>
+        <v>-1.6086</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0202</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9186</v>
+        <v>-0.3854</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6663</v>
+        <v>0.1845</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2523</v>
+        <v>-0.5699</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3858</v>
+        <v>-1.9697</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.618</v>
+        <v>-1.7931</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7678</v>
+        <v>-0.1766</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0382</v>
+        <v>-3.7057</v>
       </c>
       <c r="R24" t="n">
-        <v>2.594</v>
+        <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9953</v>
+        <v>0.4663</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8207</v>
+        <v>0.3246</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1746</v>
+        <v>0.1418</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6014</v>
+        <v>-4.6015</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.0069</v>
+        <v>-5.0068</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4052</v>
+        <v>0.4052999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>3.032200000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>6.949299999999999</v>
+        <v>6.949299999999998</v>
       </c>
       <c r="I25" t="n">
         <v>-3.9171</v>
@@ -2395,7 +2395,7 @@
         <v>-3.9542</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.558699999999999</v>
+        <v>-5.5587</v>
       </c>
       <c r="Q25" t="n">
         <v>-25.0137</v>
@@ -2404,13 +2404,13 @@
         <v>19.4551</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4414000000000001</v>
+        <v>0.4414</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3309</v>
+        <v>1.3308</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8890999999999999</v>
+        <v>-0.8891999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5166</v>
